--- a/dirasakan_bulanan.xlsx
+++ b/dirasakan_bulanan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Seismioto\Pengolahan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644347F7-E901-456B-A4EE-32BC60498B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E52A10-F4E7-431C-9D00-AC8F057D337F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4545" yWindow="1815" windowWidth="12450" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -18,26 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$H$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>Tanggal</t>
   </si>
@@ -63,24 +49,43 @@
     <t>Dirasakan</t>
   </si>
   <si>
-    <t>22 km Tenggara Karangasem-Bali</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Kab. Karangasem III MMI</t>
+    <t>23 km Tenggara Karangasem-Bali</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Karangasem II - III MMI</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Karangasem II MMI</t>
+  </si>
+  <si>
+    <t>10:52:50</t>
+  </si>
+  <si>
+    <t>63 km Tenggara Kuta Selatan-Bali</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kota Denpasar, Kab. Badung, Kab. Lombok Tengah, Kab. Lombok Barat, Kota Mataram III MMI, Kab. Tabanan, Kab. Gianyar, Kab. Lombok Timur, Kab. Sumbawa, Kab. Sumbawa Barat II MMI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="h:mm:ss;@"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -103,16 +108,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,24 +436,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822B08B2-1387-4C99-A9BB-7378259DE79F}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="159" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -460,41 +468,98 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="4">
-        <v>46054</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0.85359953703703706</v>
+      <c r="A2" s="7">
+        <v>46082</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>-8.49</v>
+        <v>-9.27</v>
       </c>
       <c r="D2">
-        <v>115.66</v>
+        <v>115.53</v>
       </c>
       <c r="E2">
+        <v>75</v>
+      </c>
+      <c r="F2">
+        <v>4.7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="5">
+        <v>46104</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0.47204861111111113</v>
+      </c>
+      <c r="C3">
+        <v>-8.4700000000000006</v>
+      </c>
+      <c r="D3">
+        <v>115.69</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>2.7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
         <v>9</v>
       </c>
-      <c r="F2">
-        <v>3.5</v>
-      </c>
-      <c r="G2" s="5" t="s">
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="5">
+        <v>46107</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0.59361111111111109</v>
+      </c>
+      <c r="C4">
+        <v>-8.4700000000000006</v>
+      </c>
+      <c r="D4">
+        <v>115.69</v>
+      </c>
+      <c r="E4">
+        <v>14</v>
+      </c>
+      <c r="F4">
+        <v>2.8</v>
+      </c>
+      <c r="G4" t="s">
         <v>8</v>
       </c>
-      <c r="H2" t="s">
-        <v>9</v>
+      <c r="H4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1" xr:uid="{822B08B2-1387-4C99-A9BB-7378259DE79F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H8">
+      <sortCondition ref="D1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>